--- a/ITEST/itest.WebService/openl-repository/EPBDS-14273/EPBDS-14273/EPBDS-14273_RuleNameDescription.xlsx
+++ b/ITEST/itest.WebService/openl-repository/EPBDS-14273/EPBDS-14273/EPBDS-14273_RuleNameDescription.xlsx
@@ -396,7 +396,7 @@
     <t>Increment multiplier</t>
   </si>
   <si>
-    <t>i++</t>
+    <t>i += 1</t>
   </si>
   <si>
     <t>The Description for the Tbasic</t>
